--- a/artfynd/A 444-2021 artfynd.xlsx
+++ b/artfynd/A 444-2021 artfynd.xlsx
@@ -1006,10 +1006,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126288473</v>
+        <v>126287955</v>
       </c>
       <c r="B5" t="n">
-        <v>78973</v>
+        <v>57652</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1017,34 +1017,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>600002</v>
+        <v>600071</v>
       </c>
       <c r="R5" t="n">
-        <v>6924473</v>
+        <v>6924523</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1074,9 +1079,24 @@
           <t>2025-06-29</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>13:11</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>13:11</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett äldre spår, tecken på ett färskt spår i ett av dom äldre. På Tall.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1091,22 +1111,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126287955</v>
+        <v>126287843</v>
       </c>
       <c r="B6" t="n">
-        <v>57652</v>
+        <v>57649</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1114,16 +1134,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1143,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>600071</v>
+        <v>600040</v>
       </c>
       <c r="R6" t="n">
-        <v>6924523</v>
+        <v>6924549</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1176,24 +1196,9 @@
           <t>2025-06-29</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>13:11</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-06-29</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>13:11</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett äldre spår, tecken på ett färskt spår i ett av dom äldre. På Tall.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1208,22 +1213,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126287843</v>
+        <v>126288473</v>
       </c>
       <c r="B7" t="n">
-        <v>57649</v>
+        <v>78973</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1231,39 +1236,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>600040</v>
+        <v>600002</v>
       </c>
       <c r="R7" t="n">
-        <v>6924549</v>
+        <v>6924473</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 444-2021 artfynd.xlsx
+++ b/artfynd/A 444-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126288285</v>
       </c>
       <c r="B2" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>126288765</v>
       </c>
       <c r="B3" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>126288235</v>
       </c>
       <c r="B4" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1006,10 +1006,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126287955</v>
+        <v>126287843</v>
       </c>
       <c r="B5" t="n">
-        <v>57652</v>
+        <v>57653</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1017,16 +1017,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1046,10 +1046,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>600071</v>
+        <v>600040</v>
       </c>
       <c r="R5" t="n">
-        <v>6924523</v>
+        <v>6924549</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1079,24 +1079,9 @@
           <t>2025-06-29</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>13:11</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-06-29</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>13:11</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett äldre spår, tecken på ett färskt spår i ett av dom äldre. På Tall.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1111,22 +1096,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126287843</v>
+        <v>126287955</v>
       </c>
       <c r="B6" t="n">
-        <v>57649</v>
+        <v>57656</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1134,16 +1119,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1163,10 +1148,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>600040</v>
+        <v>600071</v>
       </c>
       <c r="R6" t="n">
-        <v>6924549</v>
+        <v>6924523</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1196,9 +1181,24 @@
           <t>2025-06-29</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>13:11</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>13:11</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett äldre spår, tecken på ett färskt spår i ett av dom äldre. På Tall.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1213,12 +1213,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1228,7 +1228,7 @@
         <v>126288473</v>
       </c>
       <c r="B7" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1325,7 +1325,7 @@
         <v>126288369</v>
       </c>
       <c r="B8" t="n">
-        <v>56844</v>
+        <v>56848</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1456,7 +1456,7 @@
         <v>126288128</v>
       </c>
       <c r="B9" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1563,7 +1563,7 @@
         <v>126288058</v>
       </c>
       <c r="B10" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1670,7 +1670,7 @@
         <v>126288463</v>
       </c>
       <c r="B11" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1787,7 +1787,7 @@
         <v>126288717</v>
       </c>
       <c r="B12" t="n">
-        <v>57649</v>
+        <v>57653</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
         <v>126288426</v>
       </c>
       <c r="B13" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1996,7 +1996,7 @@
         <v>126287968</v>
       </c>
       <c r="B14" t="n">
-        <v>91238</v>
+        <v>91242</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2093,7 +2093,7 @@
         <v>126288405</v>
       </c>
       <c r="B15" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 444-2021 artfynd.xlsx
+++ b/artfynd/A 444-2021 artfynd.xlsx
@@ -1006,10 +1006,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126287843</v>
+        <v>126288473</v>
       </c>
       <c r="B5" t="n">
-        <v>57653</v>
+        <v>78977</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1017,39 +1017,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>600040</v>
+        <v>600002</v>
       </c>
       <c r="R5" t="n">
-        <v>6924549</v>
+        <v>6924473</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1225,10 +1220,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126288473</v>
+        <v>126287843</v>
       </c>
       <c r="B7" t="n">
-        <v>78977</v>
+        <v>57653</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1236,34 +1231,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>600002</v>
+        <v>600040</v>
       </c>
       <c r="R7" t="n">
-        <v>6924473</v>
+        <v>6924549</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1453,7 +1453,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126288128</v>
+        <v>126288463</v>
       </c>
       <c r="B9" t="n">
         <v>57656</v>
@@ -1484,7 +1484,7 @@
       <c r="I9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1493,10 +1493,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>600088</v>
+        <v>600010</v>
       </c>
       <c r="R9" t="n">
-        <v>6924438</v>
+        <v>6924479</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1526,14 +1526,24 @@
           <t>2025-06-29</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>13:53</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-06-29</t>
         </is>
       </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>13:53</t>
+        </is>
+      </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1548,19 +1558,19 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126288058</v>
+        <v>126288128</v>
       </c>
       <c r="B10" t="n">
         <v>57656</v>
@@ -1591,7 +1601,7 @@
       <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1600,10 +1610,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>600104</v>
+        <v>600088</v>
       </c>
       <c r="R10" t="n">
-        <v>6924472</v>
+        <v>6924438</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1667,7 +1677,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126288463</v>
+        <v>126288058</v>
       </c>
       <c r="B11" t="n">
         <v>57656</v>
@@ -1707,10 +1717,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>600010</v>
+        <v>600104</v>
       </c>
       <c r="R11" t="n">
-        <v>6924479</v>
+        <v>6924472</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1740,24 +1750,14 @@
           <t>2025-06-29</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>13:53</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-06-29</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>13:53</t>
-        </is>
-      </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1772,12 +1772,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>

--- a/artfynd/A 444-2021 artfynd.xlsx
+++ b/artfynd/A 444-2021 artfynd.xlsx
@@ -1103,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126287955</v>
+        <v>126287843</v>
       </c>
       <c r="B6" t="n">
-        <v>57656</v>
+        <v>57653</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1114,16 +1114,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>600071</v>
+        <v>600040</v>
       </c>
       <c r="R6" t="n">
-        <v>6924523</v>
+        <v>6924549</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1176,24 +1176,9 @@
           <t>2025-06-29</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>13:11</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-06-29</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>13:11</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett äldre spår, tecken på ett färskt spår i ett av dom äldre. På Tall.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1208,22 +1193,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126287843</v>
+        <v>126287955</v>
       </c>
       <c r="B7" t="n">
-        <v>57653</v>
+        <v>57656</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1231,16 +1216,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1260,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>600040</v>
+        <v>600071</v>
       </c>
       <c r="R7" t="n">
-        <v>6924549</v>
+        <v>6924523</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1293,9 +1278,24 @@
           <t>2025-06-29</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>13:11</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>13:11</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett äldre spår, tecken på ett färskt spår i ett av dom äldre. På Tall.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1310,12 +1310,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>

--- a/artfynd/A 444-2021 artfynd.xlsx
+++ b/artfynd/A 444-2021 artfynd.xlsx
@@ -1006,10 +1006,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126288473</v>
+        <v>126287843</v>
       </c>
       <c r="B5" t="n">
-        <v>78977</v>
+        <v>57653</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1017,34 +1017,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>600002</v>
+        <v>600040</v>
       </c>
       <c r="R5" t="n">
-        <v>6924473</v>
+        <v>6924549</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1103,10 +1108,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126287843</v>
+        <v>126288473</v>
       </c>
       <c r="B6" t="n">
-        <v>57653</v>
+        <v>78977</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1114,39 +1119,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>600040</v>
+        <v>600002</v>
       </c>
       <c r="R6" t="n">
-        <v>6924549</v>
+        <v>6924473</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 444-2021 artfynd.xlsx
+++ b/artfynd/A 444-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126288285</v>
       </c>
       <c r="B2" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>126288765</v>
       </c>
       <c r="B3" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>126288235</v>
       </c>
       <c r="B4" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1006,10 +1006,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126287843</v>
+        <v>126288473</v>
       </c>
       <c r="B5" t="n">
-        <v>57653</v>
+        <v>78980</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1017,39 +1017,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>600040</v>
+        <v>600002</v>
       </c>
       <c r="R5" t="n">
-        <v>6924549</v>
+        <v>6924473</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1108,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126288473</v>
+        <v>126287843</v>
       </c>
       <c r="B6" t="n">
-        <v>78977</v>
+        <v>57654</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1119,34 +1114,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>600002</v>
+        <v>600040</v>
       </c>
       <c r="R6" t="n">
-        <v>6924473</v>
+        <v>6924549</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1208,7 +1208,7 @@
         <v>126287955</v>
       </c>
       <c r="B7" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1325,7 +1325,7 @@
         <v>126288369</v>
       </c>
       <c r="B8" t="n">
-        <v>56848</v>
+        <v>56849</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1456,7 +1456,7 @@
         <v>126288463</v>
       </c>
       <c r="B9" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1573,7 +1573,7 @@
         <v>126288128</v>
       </c>
       <c r="B10" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1680,7 +1680,7 @@
         <v>126288058</v>
       </c>
       <c r="B11" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1787,7 +1787,7 @@
         <v>126288717</v>
       </c>
       <c r="B12" t="n">
-        <v>57653</v>
+        <v>57654</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
         <v>126288426</v>
       </c>
       <c r="B13" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1996,7 +1996,7 @@
         <v>126287968</v>
       </c>
       <c r="B14" t="n">
-        <v>91242</v>
+        <v>91245</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2093,7 +2093,7 @@
         <v>126288405</v>
       </c>
       <c r="B15" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 444-2021 artfynd.xlsx
+++ b/artfynd/A 444-2021 artfynd.xlsx
@@ -1103,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126287843</v>
+        <v>126287955</v>
       </c>
       <c r="B6" t="n">
-        <v>57654</v>
+        <v>57657</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1114,16 +1114,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>600040</v>
+        <v>600071</v>
       </c>
       <c r="R6" t="n">
-        <v>6924549</v>
+        <v>6924523</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1176,9 +1176,24 @@
           <t>2025-06-29</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>13:11</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>13:11</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett äldre spår, tecken på ett färskt spår i ett av dom äldre. På Tall.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1193,22 +1208,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126287955</v>
+        <v>126287843</v>
       </c>
       <c r="B7" t="n">
-        <v>57657</v>
+        <v>57654</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1216,16 +1231,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1245,10 +1260,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>600071</v>
+        <v>600040</v>
       </c>
       <c r="R7" t="n">
-        <v>6924523</v>
+        <v>6924549</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1278,24 +1293,9 @@
           <t>2025-06-29</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>13:11</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-06-29</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>13:11</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett äldre spår, tecken på ett färskt spår i ett av dom äldre. På Tall.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1310,12 +1310,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>

--- a/artfynd/A 444-2021 artfynd.xlsx
+++ b/artfynd/A 444-2021 artfynd.xlsx
@@ -1103,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126287955</v>
+        <v>126287843</v>
       </c>
       <c r="B6" t="n">
-        <v>57657</v>
+        <v>57654</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1114,16 +1114,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>600071</v>
+        <v>600040</v>
       </c>
       <c r="R6" t="n">
-        <v>6924523</v>
+        <v>6924549</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1176,24 +1176,9 @@
           <t>2025-06-29</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>13:11</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-06-29</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>13:11</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett äldre spår, tecken på ett färskt spår i ett av dom äldre. På Tall.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1208,22 +1193,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126287843</v>
+        <v>126287955</v>
       </c>
       <c r="B7" t="n">
-        <v>57654</v>
+        <v>57657</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1231,16 +1216,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1260,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>600040</v>
+        <v>600071</v>
       </c>
       <c r="R7" t="n">
-        <v>6924549</v>
+        <v>6924523</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1293,9 +1278,24 @@
           <t>2025-06-29</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>13:11</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>13:11</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett äldre spår, tecken på ett färskt spår i ett av dom äldre. På Tall.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1310,12 +1310,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
